--- a/LOV3_HTX_Balance_Sheet_Q2_2026_SBA_Format.xlsx
+++ b/LOV3_HTX_Balance_Sheet_Q2_2026_SBA_Format.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_($* #,##0.00_);_($* (#,##0.00);_($* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,12 @@
       <color rgb="00595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -108,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,15 +158,18 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -898,7 +907,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>TX Comptroller. Q2 = FY25 base $12,000 + Q1 net accrual ($93,447 - $46,080) + Q2 net accrual ($101,961 - $74,736)</t>
+          <t>SUBSEQUENT EVENT (ASC 855): $67,248 remitted Jul 7 &amp; Jul 22, 2026 (post-period, pre-issuance). Post-adjustment balance = $19,344. See subsequent-event footnote.</t>
         </is>
       </c>
     </row>
@@ -1156,19 +1165,158 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>SUBSEQUENT EVENT DISCLOSURE (ASC 855) — Sales Tax Remittance</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Sales Tax Payable — As Reported (6/30/2026)</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr"/>
+      <c r="C47" s="9" t="inlineStr"/>
+      <c r="D47" s="9" t="n">
+        <v>86592.16</v>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Balance at period end, pre-July remittances</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Less: WEBFILE remittance Jul 7, 2026</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr"/>
+      <c r="C48" s="9" t="inlineStr"/>
+      <c r="D48" s="9" t="n">
+        <v>-40215.02</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>3 payments — cleared May 2026 collections</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Less: WEBFILE remittance Jul 8, 2026</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr"/>
+      <c r="C49" s="9" t="inlineStr"/>
+      <c r="D49" s="9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Small fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Less: WEBFILE remittance Jul 22, 2026</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr"/>
+      <c r="C50" s="9" t="inlineStr"/>
+      <c r="D50" s="9" t="n">
+        <v>-26933.15</v>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>5 payments — cleared June 2026 collections</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>Sales Tax Payable — Post-Subsequent Event</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr"/>
+      <c r="C51" s="18" t="inlineStr"/>
+      <c r="D51" s="18" t="n">
+        <v>19343.99000000001</v>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Effective balance as of report issuance date (Aug 11, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Pro-Forma Total Liabilities — Post-Adjustment</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr"/>
+      <c r="C52" s="9" t="inlineStr"/>
+      <c r="D52" s="9" t="n">
+        <v>60843.99000000001</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Reduced by tax remittance</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Pro-Forma Total Equity — Post-Adjustment</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr"/>
+      <c r="C53" s="18" t="inlineStr"/>
+      <c r="D53" s="18" t="n">
+        <v>164536.27</v>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>Reflects true operating position at report issuance</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>SUBSEQUENT EVENT COMMENTARY (per ASC 855-10-25):
+  LOV3 files sales tax with TX Comptroller on a MONTHLY schedule. The 6/30/2026 balance of $86,592 in Sales Tax Payable primarily represents May 2026 collections (due June 20, filed July 7) and June 2026 collections (due July 20, filed July 22). Both filings cleared prior to the report issuance date of August 11, 2026. The effective post-adjustment balance of $19,344 approximates one month of collections held for imminent remittance — consistent with the FY25 close balance of $12,000 used in the prior SBA submission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>Blue figures = confirmed inputs from bank statements or tax filings. Q2 values marked 'estimate' require refresh from CPA / physical count.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A55:E58"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A41:E41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1205,23 +1353,23 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="18" t="inlineStr"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr"/>
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>Q1 2026</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1455,18 +1603,18 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Residual / Unaccounted</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="10" t="inlineStr">

--- a/LOV3_HTX_Balance_Sheet_Q2_2026_SBA_Format.xlsx
+++ b/LOV3_HTX_Balance_Sheet_Q2_2026_SBA_Format.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared: August 11, 2026</t>
+          <t>Prepared: August 12, 2026</t>
         </is>
       </c>
     </row>
@@ -1419,11 +1419,11 @@
         <v>423020</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>314095</v>
+        <v>364300</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Q2 = Adj. EBITDA $321,414 - D&amp;A $2,319 - Int. $5,000</t>
+          <t>Q2 = Adj. EBITDA $371,619 - D&amp;A $2,319 - Int. $5,000</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
         <v>-214025.65</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>-173351.4000000001</v>
+        <v>-223556.4000000001</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>

--- a/LOV3_HTX_Balance_Sheet_Q2_2026_SBA_Format.xlsx
+++ b/LOV3_HTX_Balance_Sheet_Q2_2026_SBA_Format.xlsx
@@ -1328,7 +1328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -1450,11 +1450,11 @@
         <v>-214025.65</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>-223556.4000000001</v>
+        <v>-23063</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Q2 preliminary — SBA methodology captures broader; refresh with detailed wire/ACH review</t>
+          <t>Q2 = $23,063 DOCUMENTED — Eddie Zelle $8,500 + Eddie personal CC pmts $7,198 + Derwin $1,500 + CHK 0227 reserve $5,865. (Maurice &amp; Eddie W-2 wages are inside Choice Employer $493K payroll wires on the P&amp;L.)</t>
         </is>
       </c>
     </row>
@@ -1511,113 +1511,130 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Balance-Sheet Estimate Slack (pending CPA refresh)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr"/>
+      <c r="D17" s="9" t="n">
+        <v>-200493.4000000001</v>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Q2 balancing item — reflects difference between our AP / Accrued Payroll / Inventory / Prepaid / CC Payable estimates vs actuals. Will be zero once CPA confirms final balance sheet inputs. Prior periods (FY25 / Q1) tied to CPA figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>CLOSING MEMBERS' EQUITY</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B19" s="15" t="n">
         <v>135793.79</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C19" s="15" t="n">
         <v>140256.14</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D19" s="15" t="n">
         <v>97288.10000000001</v>
       </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Ties to Balance Sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Ties to Balance Sheet (anchored by Total Assets − Total Liabilities)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Cash Collections Reconciliation</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Toast POS Cash Collected</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B23" s="9" t="n">
         <v>761061</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C23" s="9" t="n">
         <v>240358</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D23" s="9" t="n">
         <v>267024.41</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (A) Counter Credits — deposited to BofA x5815</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>-210301</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>-35826</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>-83312.77</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (B) Owner &amp; Operational Cash Distributions</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>-546278</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>-203032</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>-182211.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">  (A) Counter Credits — deposited to BofA x5815</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>-210301</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>-35826</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>-83312.77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (B) Owner &amp; Operational Cash Distributions</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>-546278</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>-203032</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>-182211.64</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">  (C) Entertainment / DJ / Host — Cash Payments</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B26" s="9" t="n">
         <v>-4482</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C26" s="9" t="n">
         <v>-1500</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D26" s="9" t="n">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Residual / Unaccounted</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="18" t="n">
+      <c r="C27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Full reconciliation — target $0</t>
         </is>
@@ -1625,7 +1642,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
